--- a/doc/設定値と周長誤差.xlsx
+++ b/doc/設定値と周長誤差.xlsx
@@ -2,19 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{051C59C0-C3C7-4908-902A-0D2DA2A52C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4A0310-B4D0-494B-9A2D-A1FED917862E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{84F89900-73C7-49F2-8FD4-6011E42FA839}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,8 +33,33 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>hp</author>
+  </authors>
+  <commentList>
+    <comment ref="Y3" authorId="0" shapeId="0" xr:uid="{1CFFB9ED-04AF-4F7B-BA52-D3B416AECCFF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>巻かれた箔ロウを伸ばしてスケールで計測し目視でメモリを読んだ数字です。</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
   <si>
     <t>rCutDegOfst[0]</t>
     <phoneticPr fontId="1"/>
@@ -234,6 +258,215 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箔ロウ長さ[mm]</t>
+    <rPh sb="0" eb="1">
+      <t>ハク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始角度を平板を360°巻いた後を0°に設定。Xロールタワーが旧式に変更。</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヒライタ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>キュウシキ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自重</t>
+    <rPh sb="0" eb="2">
+      <t>ジジュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>開始位置[deg</t>
+    <rPh sb="0" eb="2">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>溶接余丁[mm]</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヨチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平板溶接余丁なし。溶接不可停止。</t>
+    <rPh sb="0" eb="2">
+      <t>ヒライタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨチョウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>テイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期予測地点</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ヨソクチテン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>差</t>
+    <rPh sb="0" eb="1">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>補正なし。溶接余丁なし。</t>
+    <rPh sb="0" eb="2">
+      <t>ホセイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヨチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期板厚[mm]</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>イタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>アツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>波板切る前動作で波板供給なし停止発生。</t>
+    <rPh sb="0" eb="2">
+      <t>ナミイタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ナミイタ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キョウキュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>テイシ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>波板検索終了後手動停止。</t>
+    <rPh sb="0" eb="2">
+      <t>ナミイタ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>シュウリョウゴ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>シュドウテイシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計測演算で分解能における記録絶対角度を修正。溶接不可。</t>
+    <rPh sb="0" eb="2">
+      <t>ケイソク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ブンカイノウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ゼッタイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ヨウセツ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>フカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -242,13 +475,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="180" formatCode="0.0000_ ;[Red]\-0.0000\ "/>
-    <numFmt numFmtId="181" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="183" formatCode="yy/mm/dd\ hh:mm:ss"/>
-    <numFmt numFmtId="184" formatCode="\+0_ ;[Red]\-0\ "/>
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="0.0000_ ;[Red]\-0.0000\ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="178" formatCode="yy/mm/dd\ hh:mm:ss"/>
+    <numFmt numFmtId="179" formatCode="\+0_ ;[Red]\-0\ "/>
+    <numFmt numFmtId="183" formatCode="\+0.000_ ;[Red]\-0.000\ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,6 +497,14 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -287,20 +529,38 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -616,97 +876,187 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1224BFC6-F08F-49E9-90C9-83D80FE6E6A2}">
-  <dimension ref="A1:O26"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1224BFC6-F08F-49E9-90C9-83D80FE6E6A2}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="2" max="4" width="11.08203125" customWidth="1"/>
-    <col min="5" max="8" width="15.58203125" style="4" customWidth="1"/>
-    <col min="9" max="12" width="15.58203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.58203125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="94.1640625" customWidth="1"/>
-    <col min="15" max="15" width="17.9140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="8.58203125" customWidth="1"/>
+    <col min="7" max="10" width="12.58203125" style="4" customWidth="1"/>
+    <col min="11" max="14" width="10.58203125" customWidth="1"/>
+    <col min="15" max="18" width="10.58203125" style="1" customWidth="1"/>
+    <col min="19" max="22" width="10.58203125" customWidth="1"/>
+    <col min="23" max="25" width="15.58203125" style="2" customWidth="1"/>
+    <col min="26" max="26" width="59.33203125" customWidth="1"/>
+    <col min="27" max="27" width="17.9140625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="I1" s="1" t="s">
+    <row r="1" spans="1:27" s="5" customFormat="1">
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="E2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="AA1" s="9"/>
+    </row>
+    <row r="2" spans="1:27" s="5" customFormat="1">
+      <c r="G2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="N2" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
+      <c r="O2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="8"/>
+      <c r="X2" s="8"/>
+      <c r="Y2" s="8"/>
+      <c r="AA2" s="9"/>
+    </row>
+    <row r="3" spans="1:27" s="5" customFormat="1">
+      <c r="A3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="S3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="W3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="N3" t="s">
+      <c r="X3" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="AA3" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>0</v>
       </c>
@@ -719,29 +1069,51 @@
       <c r="D4">
         <v>0.09</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
+        <v>1.29</v>
+      </c>
+      <c r="F4">
+        <v>160</v>
+      </c>
+      <c r="G4" s="4">
         <v>120</v>
       </c>
-      <c r="F4" s="4">
+      <c r="H4" s="4">
         <v>240</v>
       </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
         <v>130</v>
       </c>
-      <c r="M4" s="2">
+      <c r="S4" s="10" t="str">
+        <f>IF(AND(LEN(K4),LEN(O4)),O4-K4,"")</f>
+        <v/>
+      </c>
+      <c r="T4" s="10" t="str">
+        <f t="shared" ref="T4:V19" si="0">IF(AND(LEN(L4),LEN(P4)),P4-L4,"")</f>
+        <v/>
+      </c>
+      <c r="U4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W4" s="2">
         <v>164.08</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Z4" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="3">
+      <c r="AA4" s="3">
         <v>46049.698611111111</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>1</v>
       </c>
@@ -754,26 +1126,48 @@
       <c r="D5">
         <v>0.09</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5">
+        <v>1.29</v>
+      </c>
+      <c r="F5">
+        <v>160</v>
+      </c>
+      <c r="G5" s="4">
         <v>80</v>
       </c>
-      <c r="F5" s="4">
+      <c r="H5" s="4">
         <v>200</v>
       </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
         <v>90</v>
       </c>
-      <c r="M5" s="2">
+      <c r="S5" s="10" t="str">
+        <f t="shared" ref="S5:S42" si="1">IF(AND(LEN(K5),LEN(O5)),O5-K5,"")</f>
+        <v/>
+      </c>
+      <c r="T5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W5" s="2">
         <v>163.11000000000001</v>
       </c>
-      <c r="O5" s="3">
+      <c r="AA5" s="3">
         <v>46049.7</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>2</v>
       </c>
@@ -786,26 +1180,48 @@
       <c r="D6">
         <v>0.09</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6">
+        <v>1.29</v>
+      </c>
+      <c r="F6">
+        <v>160</v>
+      </c>
+      <c r="G6" s="4">
         <v>20</v>
       </c>
-      <c r="F6" s="4">
+      <c r="H6" s="4">
         <v>140</v>
       </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
         <v>30</v>
       </c>
-      <c r="M6" s="2">
+      <c r="S6" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W6" s="2">
         <v>162.07</v>
       </c>
-      <c r="O6" s="3">
+      <c r="AA6" s="3">
         <v>46049.701388888891</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>3</v>
       </c>
@@ -818,29 +1234,51 @@
       <c r="D7">
         <v>0.09</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7">
+        <v>1.29</v>
+      </c>
+      <c r="F7">
+        <v>160</v>
+      </c>
+      <c r="G7" s="4">
         <v>20</v>
       </c>
-      <c r="F7" s="4">
+      <c r="H7" s="4">
         <v>140</v>
       </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
         <v>30</v>
       </c>
-      <c r="M7" s="2">
+      <c r="S7" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W7" s="2">
         <v>163.5</v>
       </c>
-      <c r="N7" t="s">
+      <c r="Z7" t="s">
         <v>8</v>
       </c>
-      <c r="O7" s="3">
+      <c r="AA7" s="3">
         <v>46049.701388888891</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>4</v>
       </c>
@@ -853,29 +1291,51 @@
       <c r="D8">
         <v>0.09</v>
       </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E8">
+        <v>1.29</v>
+      </c>
+      <c r="F8">
+        <v>160</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
         <v>120</v>
       </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2">
+      <c r="I8" s="4">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W8" s="2">
         <v>159.44999999999999</v>
       </c>
-      <c r="N8" t="s">
+      <c r="Z8" t="s">
         <v>10</v>
       </c>
-      <c r="O8" s="3">
+      <c r="AA8" s="3">
         <v>46049.712500000001</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>5</v>
       </c>
@@ -888,29 +1348,51 @@
       <c r="D9">
         <v>0.09</v>
       </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9">
+        <v>1.29</v>
+      </c>
+      <c r="F9">
+        <v>160</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
         <v>120</v>
       </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2">
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="S9" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W9" s="2">
         <v>162.94999999999999</v>
       </c>
-      <c r="N9" t="s">
+      <c r="Z9" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="3">
+      <c r="AA9" s="3">
         <v>46049.715277777781</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>6</v>
       </c>
@@ -923,29 +1405,51 @@
       <c r="D10">
         <v>0.09</v>
       </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10">
+        <v>1.29</v>
+      </c>
+      <c r="F10">
+        <v>160</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
         <v>120</v>
       </c>
-      <c r="G10" s="4">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2">
+      <c r="I10" s="4">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="S10" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W10" s="2">
         <v>163.18</v>
       </c>
-      <c r="N10" t="s">
+      <c r="Z10" t="s">
         <v>13</v>
       </c>
-      <c r="O10" s="3">
+      <c r="AA10" s="3">
         <v>46049.74722222222</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>7</v>
       </c>
@@ -958,38 +1462,60 @@
       <c r="D11">
         <v>0.09</v>
       </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11">
+        <v>1.29</v>
+      </c>
+      <c r="F11">
+        <v>160</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
         <v>120</v>
       </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
         <v>6441.8040000000001</v>
       </c>
-      <c r="J11" s="1">
+      <c r="P11" s="1">
         <v>6765.5649999999996</v>
       </c>
-      <c r="K11" s="1">
+      <c r="Q11" s="1">
         <v>6470.3549999999996</v>
       </c>
-      <c r="L11" s="1">
+      <c r="R11" s="1">
         <v>7191.3549999999996</v>
       </c>
-      <c r="M11" s="2">
+      <c r="S11" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W11" s="2">
         <v>162.97</v>
       </c>
-      <c r="O11" s="3">
+      <c r="AA11" s="3">
         <v>46049.781944444447</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>8</v>
       </c>
@@ -1002,38 +1528,60 @@
       <c r="D12">
         <v>0.09</v>
       </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="E12">
+        <v>1.29</v>
+      </c>
+      <c r="F12">
+        <v>160</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
         <v>120</v>
       </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
         <v>6434.6409999999996</v>
       </c>
-      <c r="J12" s="1">
+      <c r="P12" s="1">
         <v>6758.3959999999997</v>
       </c>
-      <c r="K12" s="1">
+      <c r="Q12" s="1">
         <v>6464.1729999999998</v>
       </c>
-      <c r="L12" s="1">
+      <c r="R12" s="1">
         <v>7184.1729999999998</v>
       </c>
-      <c r="M12" s="2">
+      <c r="S12" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W12" s="2">
         <v>163.02000000000001</v>
       </c>
-      <c r="O12" s="3">
+      <c r="AA12" s="3">
         <v>46049.977083333331</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>9</v>
       </c>
@@ -1046,26 +1594,48 @@
       <c r="D13">
         <v>0.09</v>
       </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13">
+        <v>1.29</v>
+      </c>
+      <c r="F13">
+        <v>160</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
         <v>120</v>
       </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="M13" s="2">
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="S13" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W13" s="2">
         <v>163.11000000000001</v>
       </c>
-      <c r="O13" s="3">
+      <c r="AA13" s="3">
         <v>46049.977083333331</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>10</v>
       </c>
@@ -1078,38 +1648,63 @@
       <c r="D14">
         <v>0.09</v>
       </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14">
+        <v>1.29</v>
+      </c>
+      <c r="F14">
+        <v>160</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
         <v>120</v>
       </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="1">
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="1">
         <v>6430.4409999999998</v>
       </c>
-      <c r="J14" s="1">
+      <c r="P14" s="1">
         <v>6786.7839999999997</v>
       </c>
-      <c r="K14" s="1">
+      <c r="Q14" s="1">
         <v>6411.6260000000002</v>
       </c>
-      <c r="L14" s="1">
+      <c r="R14" s="1">
         <v>7131.6260000000002</v>
       </c>
-      <c r="M14" s="2">
+      <c r="S14" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W14" s="2">
         <v>163.72</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Y14" s="2">
+        <v>164</v>
+      </c>
+      <c r="AA14" s="3">
         <v>46049.977083333331</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>11</v>
       </c>
@@ -1122,38 +1717,63 @@
       <c r="D15">
         <v>0.09</v>
       </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15">
+        <v>1.29</v>
+      </c>
+      <c r="F15">
+        <v>160</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
         <v>120</v>
       </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="1">
+      <c r="I15" s="4">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="1">
         <v>6473.4369999999999</v>
       </c>
-      <c r="J15" s="1">
+      <c r="P15" s="1">
         <v>6829.7579999999998</v>
       </c>
-      <c r="K15" s="1">
+      <c r="Q15" s="1">
         <v>6454.6480000000001</v>
       </c>
-      <c r="L15" s="1">
+      <c r="R15" s="1">
         <v>7174.6480000000001</v>
       </c>
-      <c r="M15" s="2">
+      <c r="S15" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="T15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="U15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="V15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="W15" s="2">
         <v>163.92</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Y15" s="2">
+        <v>164.2</v>
+      </c>
+      <c r="AA15" s="3">
         <v>46049.977083333331</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>12</v>
       </c>
@@ -1166,41 +1786,78 @@
       <c r="D16">
         <v>0.09</v>
       </c>
-      <c r="E16" s="4">
-        <v>-20</v>
-      </c>
-      <c r="F16" s="4">
-        <v>80</v>
+      <c r="E16">
+        <v>1.29</v>
+      </c>
+      <c r="F16">
+        <v>160</v>
       </c>
       <c r="G16" s="4">
         <v>-20</v>
       </c>
       <c r="H16" s="4">
-        <v>0</v>
-      </c>
-      <c r="I16" s="1">
+        <v>80</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>-20</v>
+      </c>
+      <c r="K16">
+        <v>6140.0839999999998</v>
+      </c>
+      <c r="L16">
+        <v>6443.8379999999997</v>
+      </c>
+      <c r="M16">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N16">
+        <v>6889.6109999999999</v>
+      </c>
+      <c r="O16" s="1">
         <v>6407.2629999999999</v>
       </c>
-      <c r="J16" s="1">
+      <c r="P16" s="1">
         <v>6743.5060000000003</v>
       </c>
-      <c r="K16" s="1">
+      <c r="Q16" s="1">
         <v>6408.5640000000003</v>
       </c>
-      <c r="L16" s="1">
+      <c r="R16" s="1">
         <v>7108.5640000000003</v>
       </c>
-      <c r="M16" s="2">
+      <c r="S16" s="10">
+        <f t="shared" si="1"/>
+        <v>267.17900000000009</v>
+      </c>
+      <c r="T16" s="10">
+        <f t="shared" si="0"/>
+        <v>299.66800000000057</v>
+      </c>
+      <c r="U16" s="10">
+        <f t="shared" si="0"/>
+        <v>218.95300000000043</v>
+      </c>
+      <c r="V16" s="10">
+        <f t="shared" si="0"/>
+        <v>218.95300000000043</v>
+      </c>
+      <c r="W16" s="2">
         <v>163.25</v>
       </c>
-      <c r="N16" t="s">
+      <c r="Y16" s="2">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="Z16" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="3">
+      <c r="AA16" s="3">
         <v>46049.977083333331</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:27">
       <c r="A17">
         <v>13</v>
       </c>
@@ -1213,38 +1870,75 @@
       <c r="D17">
         <v>0.09</v>
       </c>
-      <c r="E17" s="4">
-        <v>-60</v>
-      </c>
-      <c r="F17" s="4">
-        <v>20</v>
+      <c r="E17">
+        <v>1.29</v>
+      </c>
+      <c r="F17">
+        <v>160</v>
       </c>
       <c r="G17" s="4">
         <v>-60</v>
       </c>
       <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="I17" s="1">
+        <v>20</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4">
+        <v>-60</v>
+      </c>
+      <c r="K17">
+        <v>6100.0839999999998</v>
+      </c>
+      <c r="L17">
+        <v>6383.8379999999997</v>
+      </c>
+      <c r="M17">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N17">
+        <v>6849.6109999999999</v>
+      </c>
+      <c r="O17" s="1">
         <v>6380.9930000000004</v>
       </c>
-      <c r="J17" s="1">
+      <c r="P17" s="1">
         <v>6697.424</v>
       </c>
-      <c r="K17" s="1">
+      <c r="Q17" s="1">
         <v>6422.0739999999996</v>
       </c>
-      <c r="L17" s="1">
+      <c r="R17" s="1">
         <v>7082.0739999999996</v>
       </c>
-      <c r="M17" s="2">
+      <c r="S17" s="10">
+        <f t="shared" si="1"/>
+        <v>280.90900000000056</v>
+      </c>
+      <c r="T17" s="10">
+        <f t="shared" si="0"/>
+        <v>313.58600000000024</v>
+      </c>
+      <c r="U17" s="10">
+        <f t="shared" si="0"/>
+        <v>232.46299999999974</v>
+      </c>
+      <c r="V17" s="10">
+        <f t="shared" si="0"/>
+        <v>232.46299999999974</v>
+      </c>
+      <c r="W17" s="2">
         <v>162.38</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Y17" s="2">
+        <v>162.80000000000001</v>
+      </c>
+      <c r="AA17" s="3">
         <v>46049.977083333331</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:27">
       <c r="A18">
         <v>14</v>
       </c>
@@ -1257,98 +1951,1126 @@
       <c r="D18">
         <v>0.09</v>
       </c>
-      <c r="E18" s="4">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="4">
-        <v>20</v>
+      <c r="E18">
+        <v>1.29</v>
+      </c>
+      <c r="F18">
+        <v>160</v>
       </c>
       <c r="G18" s="4">
         <v>-100</v>
       </c>
       <c r="H18" s="4">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
+        <v>20</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>-100</v>
+      </c>
+      <c r="K18" s="4">
+        <v>6060.0839999999998</v>
+      </c>
+      <c r="L18">
+        <v>6383.8379999999997</v>
+      </c>
+      <c r="M18">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N18">
+        <v>6809.6109999999999</v>
+      </c>
+      <c r="O18" s="1">
         <v>6363.768</v>
       </c>
-      <c r="J18" s="1">
+      <c r="P18" s="1">
         <v>6720.2629999999999</v>
       </c>
-      <c r="K18" s="1">
+      <c r="Q18" s="1">
         <v>6444.7719999999999</v>
       </c>
-      <c r="L18" s="1">
+      <c r="R18" s="1">
         <v>7064.7719999999999</v>
       </c>
-      <c r="M18" s="2">
+      <c r="S18" s="10">
+        <f t="shared" si="1"/>
+        <v>303.6840000000002</v>
+      </c>
+      <c r="T18" s="10">
+        <f t="shared" si="0"/>
+        <v>336.42500000000018</v>
+      </c>
+      <c r="U18" s="10">
+        <f t="shared" si="0"/>
+        <v>255.16100000000006</v>
+      </c>
+      <c r="V18" s="10">
+        <f t="shared" si="0"/>
+        <v>255.16100000000006</v>
+      </c>
+      <c r="W18" s="2">
         <v>162.11000000000001</v>
       </c>
-      <c r="N18" t="s">
+      <c r="Y18" s="2">
+        <v>162.30000000000001</v>
+      </c>
+      <c r="Z18" t="s">
         <v>22</v>
       </c>
-      <c r="O18" s="3">
+      <c r="AA18" s="3">
         <v>46049.981944444444</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:27">
       <c r="A19">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19">
+        <v>50</v>
+      </c>
+      <c r="C19">
+        <v>50</v>
+      </c>
+      <c r="D19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19">
+        <v>1.29</v>
+      </c>
+      <c r="F19">
+        <v>180</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>120</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="L19">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="M19">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N19">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="O19" s="1">
+        <v>6672.4110000000001</v>
+      </c>
+      <c r="P19" s="1">
+        <v>7030.2809999999999</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>6651.3590000000004</v>
+      </c>
+      <c r="R19" s="1">
+        <v>7371.3590000000004</v>
+      </c>
+      <c r="S19" s="10">
+        <f t="shared" si="1"/>
+        <v>512.32700000000023</v>
+      </c>
+      <c r="T19" s="10">
+        <f t="shared" si="0"/>
+        <v>546.44300000000021</v>
+      </c>
+      <c r="U19" s="10">
+        <f t="shared" si="0"/>
+        <v>461.7480000000005</v>
+      </c>
+      <c r="V19" s="10">
+        <f t="shared" si="0"/>
+        <v>461.7480000000005</v>
+      </c>
+      <c r="W19" s="2">
+        <v>167.38</v>
+      </c>
+      <c r="Y19" s="2">
+        <v>167.9</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA19" s="3">
+        <v>46050.573611111111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
       <c r="A20">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20">
+        <v>50</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20">
+        <v>1.29</v>
+      </c>
+      <c r="F20">
+        <v>180</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0</v>
+      </c>
+      <c r="H20" s="4">
+        <v>120</v>
+      </c>
+      <c r="I20" s="4">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="L20">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="M20">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N20">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="O20" s="1">
+        <v>6930.07</v>
+      </c>
+      <c r="P20" s="1">
+        <v>7288.0209999999997</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>6908.9250000000002</v>
+      </c>
+      <c r="R20" s="1">
+        <v>7628.9250000000002</v>
+      </c>
+      <c r="S20" s="10">
+        <f t="shared" si="1"/>
+        <v>769.98599999999988</v>
+      </c>
+      <c r="T20" s="10">
+        <f t="shared" ref="T20:T42" si="2">IF(AND(LEN(L20),LEN(P20)),P20-L20,"")</f>
+        <v>804.18299999999999</v>
+      </c>
+      <c r="U20" s="10">
+        <f t="shared" ref="U20:U42" si="3">IF(AND(LEN(M20),LEN(Q20)),Q20-M20,"")</f>
+        <v>719.31400000000031</v>
+      </c>
+      <c r="V20" s="10">
+        <f t="shared" ref="V20:V42" si="4">IF(AND(LEN(N20),LEN(R20)),R20-N20,"")</f>
+        <v>719.31400000000031</v>
+      </c>
+      <c r="W20" s="2">
+        <v>167.31</v>
+      </c>
+      <c r="Y20" s="2">
+        <v>167.7</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>46050.57916666667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
       <c r="A21">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21">
+        <v>50</v>
+      </c>
+      <c r="C21">
+        <v>50</v>
+      </c>
+      <c r="D21" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21">
+        <v>1.29</v>
+      </c>
+      <c r="F21">
+        <v>180</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0</v>
+      </c>
+      <c r="H21" s="4">
+        <v>120</v>
+      </c>
+      <c r="I21" s="4">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="L21">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="M21">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N21">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="O21" s="1">
+        <v>6931.63</v>
+      </c>
+      <c r="P21" s="1">
+        <v>7289.5820000000003</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>6910.4849999999997</v>
+      </c>
+      <c r="R21" s="1">
+        <v>7630.4849999999997</v>
+      </c>
+      <c r="S21" s="10">
+        <f t="shared" si="1"/>
+        <v>771.54600000000028</v>
+      </c>
+      <c r="T21" s="10">
+        <f t="shared" si="2"/>
+        <v>805.7440000000006</v>
+      </c>
+      <c r="U21" s="10">
+        <f t="shared" si="3"/>
+        <v>720.8739999999998</v>
+      </c>
+      <c r="V21" s="10">
+        <f t="shared" si="4"/>
+        <v>720.8739999999998</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>167.6</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>46050.586111111108</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
       <c r="A22">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22">
+        <v>50</v>
+      </c>
+      <c r="C22">
+        <v>50</v>
+      </c>
+      <c r="D22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22">
+        <v>1.29</v>
+      </c>
+      <c r="F22">
+        <v>180</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0</v>
+      </c>
+      <c r="H22" s="4">
+        <v>120</v>
+      </c>
+      <c r="I22" s="4">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="L22">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="M22">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N22">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="O22">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="P22">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="Q22">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="R22">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="S22" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U22" s="10">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y22" s="2">
+        <v>157</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>46050.62222222222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27">
       <c r="A23">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23">
+        <v>50</v>
+      </c>
+      <c r="C23">
+        <v>50</v>
+      </c>
+      <c r="D23" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23">
+        <v>1.29</v>
+      </c>
+      <c r="F23">
+        <v>180</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4">
+        <v>120</v>
+      </c>
+      <c r="I23" s="4">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="L23">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="M23">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N23">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="O23">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="P23">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="Q23">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="R23">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="S23" s="10">
+        <f t="shared" ref="S23" si="5">IF(AND(LEN(K23),LEN(O23)),O23-K23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" ref="T23" si="6">IF(AND(LEN(L23),LEN(P23)),P23-L23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="U23" s="10">
+        <f t="shared" ref="U23" si="7">IF(AND(LEN(M23),LEN(Q23)),Q23-M23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V23" s="10">
+        <f t="shared" ref="V23" si="8">IF(AND(LEN(N23),LEN(R23)),R23-N23,"")</f>
+        <v>0</v>
+      </c>
+      <c r="X23" s="2">
+        <v>14</v>
+      </c>
+      <c r="Y23" s="2">
+        <v>153.4</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>46050.631944444445</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27">
       <c r="A24">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24">
+        <v>50</v>
+      </c>
+      <c r="C24">
+        <v>50</v>
+      </c>
+      <c r="D24" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24">
+        <v>1.29</v>
+      </c>
+      <c r="F24">
+        <v>180</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <v>120</v>
+      </c>
+      <c r="I24" s="4">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="L24">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="M24">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N24">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="O24">
+        <v>6160.0839999999998</v>
+      </c>
+      <c r="P24">
+        <v>6483.8379999999997</v>
+      </c>
+      <c r="Q24">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="R24">
+        <v>6909.6109999999999</v>
+      </c>
+      <c r="S24" s="10">
+        <f t="shared" ref="S24" si="9">IF(AND(LEN(K24),LEN(O24)),O24-K24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="T24" s="10">
+        <f t="shared" ref="T24" si="10">IF(AND(LEN(L24),LEN(P24)),P24-L24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="U24" s="10">
+        <f t="shared" ref="U24" si="11">IF(AND(LEN(M24),LEN(Q24)),Q24-M24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="10">
+        <f t="shared" ref="V24" si="12">IF(AND(LEN(N24),LEN(R24)),R24-N24,"")</f>
+        <v>0</v>
+      </c>
+      <c r="X24" s="2">
+        <v>-16</v>
+      </c>
+      <c r="Y24" s="2">
+        <v>155.5</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>46050.636111111111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27">
       <c r="A25">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25">
+        <v>50</v>
+      </c>
+      <c r="C25">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25">
+        <v>1.29</v>
+      </c>
+      <c r="F25">
+        <v>180</v>
+      </c>
+      <c r="G25" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H25" s="4">
+        <v>20</v>
+      </c>
+      <c r="I25" s="4">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>-100</v>
+      </c>
+      <c r="K25">
+        <v>6060.0839999999998</v>
+      </c>
+      <c r="L25">
+        <v>6383.8379999999997</v>
+      </c>
+      <c r="M25">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N25">
+        <v>6809.6109999999999</v>
+      </c>
+      <c r="O25" s="1">
+        <v>6753.8130000000001</v>
+      </c>
+      <c r="P25" s="1">
+        <v>7111.3130000000001</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>6833.1949999999997</v>
+      </c>
+      <c r="R25" s="1">
+        <v>7453.1949999999997</v>
+      </c>
+      <c r="S25" s="10">
+        <f t="shared" ref="S25:S26" si="13">IF(AND(LEN(K25),LEN(O25)),O25-K25,"")</f>
+        <v>693.72900000000027</v>
+      </c>
+      <c r="T25" s="10">
+        <f t="shared" ref="T25:T26" si="14">IF(AND(LEN(L25),LEN(P25)),P25-L25,"")</f>
+        <v>727.47500000000036</v>
+      </c>
+      <c r="U25" s="10">
+        <f t="shared" ref="U25:U26" si="15">IF(AND(LEN(M25),LEN(Q25)),Q25-M25,"")</f>
+        <v>643.58399999999983</v>
+      </c>
+      <c r="V25" s="10">
+        <f t="shared" ref="V25:V26" si="16">IF(AND(LEN(N25),LEN(R25)),R25-N25,"")</f>
+        <v>643.58399999999983</v>
+      </c>
+      <c r="W25" s="2">
+        <v>165.27</v>
+      </c>
+      <c r="X25" s="2">
+        <v>16</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>165.7</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>46050.655555555553</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27">
       <c r="A26">
         <v>22</v>
+      </c>
+      <c r="B26">
+        <v>50</v>
+      </c>
+      <c r="C26">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26">
+        <v>1.29</v>
+      </c>
+      <c r="F26">
+        <v>180</v>
+      </c>
+      <c r="G26" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H26" s="4">
+        <v>20</v>
+      </c>
+      <c r="I26" s="4">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4">
+        <v>-100</v>
+      </c>
+      <c r="K26">
+        <v>6060.0839999999998</v>
+      </c>
+      <c r="L26">
+        <v>6383.8379999999997</v>
+      </c>
+      <c r="M26">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N26">
+        <v>6809.6109999999999</v>
+      </c>
+      <c r="O26" s="1">
+        <v>6686.0630000000001</v>
+      </c>
+      <c r="P26" s="1">
+        <v>7043.5379999999996</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>6765.473</v>
+      </c>
+      <c r="R26" s="1">
+        <v>7385.473</v>
+      </c>
+      <c r="S26" s="10">
+        <f t="shared" si="13"/>
+        <v>625.97900000000027</v>
+      </c>
+      <c r="T26" s="10">
+        <f t="shared" si="14"/>
+        <v>659.69999999999982</v>
+      </c>
+      <c r="U26" s="10">
+        <f t="shared" si="15"/>
+        <v>575.86200000000008</v>
+      </c>
+      <c r="V26" s="10">
+        <f t="shared" si="16"/>
+        <v>575.86200000000008</v>
+      </c>
+      <c r="W26" s="2">
+        <v>165.37</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>165.5</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>46050.675000000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="G27" s="4">
+        <v>-100</v>
+      </c>
+      <c r="H27" s="4">
+        <v>20</v>
+      </c>
+      <c r="I27" s="4">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>-100</v>
+      </c>
+      <c r="K27">
+        <v>6060.0839999999998</v>
+      </c>
+      <c r="L27">
+        <v>6383.8379999999997</v>
+      </c>
+      <c r="M27">
+        <v>6189.6109999999999</v>
+      </c>
+      <c r="N27">
+        <v>6809.6109999999999</v>
+      </c>
+      <c r="O27" s="1">
+        <v>6686.0630000000001</v>
+      </c>
+      <c r="P27" s="1">
+        <v>7043.5379999999996</v>
+      </c>
+      <c r="Q27" s="1">
+        <v>6765.473</v>
+      </c>
+      <c r="R27" s="1">
+        <v>7385.473</v>
+      </c>
+      <c r="S27" s="10">
+        <v>6701.4170000000004</v>
+      </c>
+      <c r="T27" s="10">
+        <v>7058.8969999999999</v>
+      </c>
+      <c r="U27" s="10">
+        <v>6780.8209999999999</v>
+      </c>
+      <c r="V27" s="10">
+        <v>7400.8209999999999</v>
+      </c>
+      <c r="X27" s="2">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="2">
+        <v>166</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>46050.715277777781</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="S28" s="10" t="str">
+        <f t="shared" ref="S27:S42" si="17">IF(AND(LEN(K28),LEN(O28)),O28-K28,"")</f>
+        <v/>
+      </c>
+      <c r="T28" s="10" t="str">
+        <f t="shared" ref="T27:T42" si="18">IF(AND(LEN(L28),LEN(P28)),P28-L28,"")</f>
+        <v/>
+      </c>
+      <c r="U28" s="10" t="str">
+        <f t="shared" ref="U27:U42" si="19">IF(AND(LEN(M28),LEN(Q28)),Q28-M28,"")</f>
+        <v/>
+      </c>
+      <c r="V28" s="10" t="str">
+        <f t="shared" ref="V27:V42" si="20">IF(AND(LEN(N28),LEN(R28)),R28-N28,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:27">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="S29" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T29" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U29" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V29" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:27">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="S30" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T30" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U30" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V30" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:27">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="S31" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T31" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U31" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V31" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:27">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="S32" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T32" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U32" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V32" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="S33" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T33" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U33" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V33" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="S34" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T34" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U34" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V34" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="S35" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T35" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U35" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V35" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36">
+        <v>32</v>
+      </c>
+      <c r="S36" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T36" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U36" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V36" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
+      <c r="A37">
+        <v>33</v>
+      </c>
+      <c r="S37" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T37" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U37" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V37" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
+      <c r="A38">
+        <v>34</v>
+      </c>
+      <c r="S38" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T38" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U38" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V38" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="S39" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T39" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U39" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V39" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
+      <c r="A40">
+        <v>36</v>
+      </c>
+      <c r="S40" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T40" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U40" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V40" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
+      <c r="A41">
+        <v>37</v>
+      </c>
+      <c r="S41" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T41" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U41" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V41" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="S42" s="10" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="T42" s="10" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="U42" s="10" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="V42" s="10" t="str">
+        <f t="shared" si="20"/>
+        <v/>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC510F5C-D4F5-4205-9DCC-E6E2B5C399DF}">
-  <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>